--- a/business_forms/021_fabric_order_form--business_forms.xlsx
+++ b/business_forms/021_fabric_order_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1056,8 +1056,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'cotton'}</t>
+          <t>cotton</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Cotton'}</t>
+          <t>Cotton</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'polyester'}</t>
+          <t>polyester</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Polyester'}</t>
+          <t>Polyester</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'wool'}</t>
+          <t>wool</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Wool'}</t>
+          <t>Wool</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'net_30'}</t>
+          <t>net_30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Net 30'}</t>
+          <t>Net 30</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'net_60'}</t>
+          <t>net_60</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Net 60'}</t>
+          <t>Net 60</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'prepay'}</t>
+          <t>prepay</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Prepay'}</t>
+          <t>Prepay</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'customer'}</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Customer'}</t>
+          <t>Customer</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'supplier'}</t>
+          <t>supplier</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Supplier'}</t>
+          <t>Supplier</t>
         </is>
       </c>
     </row>
